--- a/Overpotnital/Air/BOL/Edited/KB Polyol air_edited.xlsx
+++ b/Overpotnital/Air/BOL/Edited/KB Polyol air_edited.xlsx
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="S4" s="0" t="n">
-        <v>-0.48</v>
+        <v>-0.515</v>
       </c>
       <c r="V4" s="0" t="n">
         <v>-6</v>
@@ -7122,10 +7122,10 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" t="n">
+      <c r="A97" s="0" t="n">
         <v>3.49156865</v>
       </c>
-      <c r="B97" t="n">
+      <c r="B97" s="0" t="n">
         <v>0.44894</v>
       </c>
       <c r="C97" s="0">
@@ -7189,10 +7189,10 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" t="n">
+      <c r="A98" s="0" t="n">
         <v>3.52823025</v>
       </c>
-      <c r="B98" t="n">
+      <c r="B98" s="0" t="n">
         <v>0.44509</v>
       </c>
       <c r="C98" s="0">
@@ -7256,10 +7256,10 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" t="n">
+      <c r="A99" s="0" t="n">
         <v>3.56599125</v>
       </c>
-      <c r="B99" t="n">
+      <c r="B99" s="0" t="n">
         <v>0.4414</v>
       </c>
       <c r="C99" s="0">
@@ -7323,10 +7323,10 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" t="n">
+      <c r="A100" s="0" t="n">
         <v>3.6033852</v>
       </c>
-      <c r="B100" t="n">
+      <c r="B100" s="0" t="n">
         <v>0.43748</v>
       </c>
       <c r="C100" s="0">
@@ -7390,10 +7390,10 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" t="n">
+      <c r="A101" s="0" t="n">
         <v>3.6407802</v>
       </c>
-      <c r="B101" t="n">
+      <c r="B101" s="0" t="n">
         <v>0.43358</v>
       </c>
       <c r="C101" s="0">
@@ -7457,10 +7457,10 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" t="n">
+      <c r="A102" s="0" t="n">
         <v>3.6770745</v>
       </c>
-      <c r="B102" t="n">
+      <c r="B102" s="0" t="n">
         <v>0.43002</v>
       </c>
       <c r="C102" s="0">
@@ -7524,10 +7524,10 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" t="n">
+      <c r="A103" s="0" t="n">
         <v>3.71336905</v>
       </c>
-      <c r="B103" t="n">
+      <c r="B103" s="0" t="n">
         <v>0.42597</v>
       </c>
       <c r="C103" s="0">
@@ -7591,10 +7591,10 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" t="n">
+      <c r="A104" s="0" t="n">
         <v>3.75149705</v>
       </c>
-      <c r="B104" t="n">
+      <c r="B104" s="0" t="n">
         <v>0.42175</v>
       </c>
       <c r="C104" s="0">
@@ -7658,10 +7658,10 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" t="n">
+      <c r="A105" s="0" t="n">
         <v>3.78852435</v>
       </c>
-      <c r="B105" t="n">
+      <c r="B105" s="0" t="n">
         <v>0.4176</v>
       </c>
       <c r="C105" s="0">
@@ -7725,10 +7725,10 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" t="n">
+      <c r="A106" s="0" t="n">
         <v>3.82555265</v>
       </c>
-      <c r="B106" t="n">
+      <c r="B106" s="0" t="n">
         <v>0.41308</v>
       </c>
       <c r="C106" s="0">
@@ -7792,10 +7792,10 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" t="n">
+      <c r="A107" s="0" t="n">
         <v>3.8633133</v>
       </c>
-      <c r="B107" t="n">
+      <c r="B107" s="0" t="n">
         <v>0.40907</v>
       </c>
       <c r="C107" s="0">
@@ -7859,10 +7859,10 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" t="n">
+      <c r="A108" s="0" t="n">
         <v>3.90070755</v>
       </c>
-      <c r="B108" t="n">
+      <c r="B108" s="0" t="n">
         <v>0.40493</v>
       </c>
       <c r="C108" s="0">
@@ -7926,10 +7926,10 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" t="n">
+      <c r="A109" s="0" t="n">
         <v>3.93773585</v>
       </c>
-      <c r="B109" t="n">
+      <c r="B109" s="0" t="n">
         <v>0.40059</v>
       </c>
       <c r="C109" s="0">
@@ -7993,10 +7993,10 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" t="n">
+      <c r="A110" s="0" t="n">
         <v>3.9769629</v>
       </c>
-      <c r="B110" t="n">
+      <c r="B110" s="0" t="n">
         <v>0.39586</v>
       </c>
       <c r="C110" s="0">
@@ -8060,10 +8060,10 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" t="n">
+      <c r="A111" s="0" t="n">
         <v>4.01692355</v>
       </c>
-      <c r="B111" t="n">
+      <c r="B111" s="0" t="n">
         <v>0.39138</v>
       </c>
       <c r="C111" s="0">
@@ -8127,10 +8127,10 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" t="n">
+      <c r="A112" s="0" t="n">
         <v>4.0535849</v>
       </c>
-      <c r="B112" t="n">
+      <c r="B112" s="0" t="n">
         <v>0.38633</v>
       </c>
       <c r="C112" s="0">
@@ -8194,10 +8194,10 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" t="n">
+      <c r="A113" s="0" t="n">
         <v>4.08987985</v>
       </c>
-      <c r="B113" t="n">
+      <c r="B113" s="0" t="n">
         <v>0.38169</v>
       </c>
       <c r="C113" s="0">
@@ -8261,10 +8261,10 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" t="n">
+      <c r="A114" s="0" t="n">
         <v>4.12617415</v>
       </c>
-      <c r="B114" t="n">
+      <c r="B114" s="0" t="n">
         <v>0.37708</v>
       </c>
       <c r="C114" s="0">
@@ -8328,10 +8328,10 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" t="n">
+      <c r="A115" s="0" t="n">
         <v>4.16466805</v>
       </c>
-      <c r="B115" t="n">
+      <c r="B115" s="0" t="n">
         <v>0.37255</v>
       </c>
       <c r="C115" s="0">
@@ -8395,10 +8395,10 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" t="n">
+      <c r="A116" s="0" t="n">
         <v>4.2013294</v>
       </c>
-      <c r="B116" t="n">
+      <c r="B116" s="0" t="n">
         <v>0.36761</v>
       </c>
       <c r="C116" s="0">
@@ -8462,10 +8462,10 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" t="n">
+      <c r="A117" s="0" t="n">
         <v>4.2390907</v>
       </c>
-      <c r="B117" t="n">
+      <c r="B117" s="0" t="n">
         <v>0.36257</v>
       </c>
       <c r="C117" s="0">
@@ -8529,10 +8529,10 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" t="n">
+      <c r="A118" s="0" t="n">
         <v>4.276485</v>
       </c>
-      <c r="B118" t="n">
+      <c r="B118" s="0" t="n">
         <v>0.35769</v>
       </c>
       <c r="C118" s="0">
@@ -8596,10 +8596,10 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" t="n">
+      <c r="A119" s="0" t="n">
         <v>4.3131463</v>
       </c>
-      <c r="B119" t="n">
+      <c r="B119" s="0" t="n">
         <v>0.35286</v>
       </c>
       <c r="C119" s="0">
@@ -8663,10 +8663,10 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" t="n">
+      <c r="A120" s="0" t="n">
         <v>4.3512739</v>
       </c>
-      <c r="B120" t="n">
+      <c r="B120" s="0" t="n">
         <v>0.34819</v>
       </c>
       <c r="C120" s="0">
@@ -8730,10 +8730,10 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" t="n">
+      <c r="A121" s="0" t="n">
         <v>4.38756855</v>
       </c>
-      <c r="B121" t="n">
+      <c r="B121" s="0" t="n">
         <v>0.3431</v>
       </c>
       <c r="C121" s="0">
@@ -8797,10 +8797,10 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" t="n">
+      <c r="A122" s="0" t="n">
         <v>4.4256962</v>
       </c>
-      <c r="B122" t="n">
+      <c r="B122" s="0" t="n">
         <v>0.33785</v>
       </c>
       <c r="C122" s="0">
@@ -8864,10 +8864,10 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" t="n">
+      <c r="A123" s="0" t="n">
         <v>4.46235755</v>
       </c>
-      <c r="B123" t="n">
+      <c r="B123" s="0" t="n">
         <v>0.33281</v>
       </c>
       <c r="C123" s="0">
@@ -8931,10 +8931,10 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" t="n">
+      <c r="A124" s="0" t="n">
         <v>4.4993851</v>
       </c>
-      <c r="B124" t="n">
+      <c r="B124" s="0" t="n">
         <v>0.32817</v>
       </c>
       <c r="C124" s="0">
@@ -8998,10 +8998,10 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" t="n">
+      <c r="A125" s="0" t="n">
         <v>4.53714645</v>
       </c>
-      <c r="B125" t="n">
+      <c r="B125" s="0" t="n">
         <v>0.32273</v>
       </c>
       <c r="C125" s="0">
@@ -9065,10 +9065,10 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" t="n">
+      <c r="A126" s="0" t="n">
         <v>4.5749067</v>
       </c>
-      <c r="B126" t="n">
+      <c r="B126" s="0" t="n">
         <v>0.31759</v>
       </c>
       <c r="C126" s="0">
@@ -9132,10 +9132,10 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" t="n">
+      <c r="A127" s="0" t="n">
         <v>4.61230135</v>
       </c>
-      <c r="B127" t="n">
+      <c r="B127" s="0" t="n">
         <v>0.31243</v>
       </c>
       <c r="C127" s="0">
@@ -9199,10 +9199,10 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" t="n">
+      <c r="A128" s="0" t="n">
         <v>4.64969565</v>
       </c>
-      <c r="B128" t="n">
+      <c r="B128" s="0" t="n">
         <v>0.30699</v>
       </c>
       <c r="C128" s="0">
@@ -9266,10 +9266,10 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" t="n">
+      <c r="A129" s="0" t="n">
         <v>4.68929</v>
       </c>
-      <c r="B129" t="n">
+      <c r="B129" s="0" t="n">
         <v>0.30242</v>
       </c>
       <c r="C129" s="0">
@@ -9333,10 +9333,10 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" t="n">
+      <c r="A130" s="0" t="n">
         <v>4.72595135</v>
       </c>
-      <c r="B130" t="n">
+      <c r="B130" s="0" t="n">
         <v>0.29685</v>
       </c>
       <c r="C130" s="0">
@@ -9400,10 +9400,10 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" t="n">
+      <c r="A131" s="0" t="n">
         <v>4.76224595</v>
       </c>
-      <c r="B131" t="n">
+      <c r="B131" s="0" t="n">
         <v>0.2921</v>
       </c>
       <c r="C131" s="0">
@@ -9467,10 +9467,10 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" t="n">
+      <c r="A132" s="0" t="n">
         <v>4.7985402</v>
       </c>
-      <c r="B132" t="n">
+      <c r="B132" s="0" t="n">
         <v>0.28687</v>
       </c>
       <c r="C132" s="0">
@@ -9534,10 +9534,10 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" t="n">
+      <c r="A133" s="0" t="n">
         <v>4.8359345</v>
       </c>
-      <c r="B133" t="n">
+      <c r="B133" s="0" t="n">
         <v>0.28166</v>
       </c>
       <c r="C133" s="0">
@@ -9601,10 +9601,10 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" t="n">
+      <c r="A134" s="0" t="n">
         <v>4.87296245</v>
       </c>
-      <c r="B134" t="n">
+      <c r="B134" s="0" t="n">
         <v>0.27664</v>
       </c>
       <c r="C134" s="0">
@@ -9668,10 +9668,10 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" t="n">
+      <c r="A135" s="0" t="n">
         <v>4.90925705</v>
       </c>
-      <c r="B135" t="n">
+      <c r="B135" s="0" t="n">
         <v>0.27151</v>
       </c>
       <c r="C135" s="0">
@@ -9735,10 +9735,10 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" t="n">
+      <c r="A136" s="0" t="n">
         <v>4.9455517</v>
       </c>
-      <c r="B136" t="n">
+      <c r="B136" s="0" t="n">
         <v>0.26644</v>
       </c>
       <c r="C136" s="0">
@@ -9802,10 +9802,10 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" t="n">
+      <c r="A137" s="0" t="n">
         <v>4.98221295</v>
       </c>
-      <c r="B137" t="n">
+      <c r="B137" s="0" t="n">
         <v>0.26132</v>
       </c>
       <c r="C137" s="0">
@@ -9869,10 +9869,10 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" t="n">
+      <c r="A138" s="0" t="n">
         <v>5.0196076</v>
       </c>
-      <c r="B138" t="n">
+      <c r="B138" s="0" t="n">
         <v>0.25598</v>
       </c>
       <c r="C138" s="0">
@@ -9936,10 +9936,10 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" t="n">
+      <c r="A139" s="0" t="n">
         <v>5.05590185</v>
       </c>
-      <c r="B139" t="n">
+      <c r="B139" s="0" t="n">
         <v>0.25049</v>
       </c>
       <c r="C139" s="0">
@@ -18914,7 +18914,7 @@
       <c r="C2" s="0" t="n">
         <v>0.846</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" s="0" t="n">
         <v>0.02188474498689175</v>
       </c>
       <c r="E2" s="0">
@@ -18970,7 +18970,7 @@
       <c r="C3" s="0" t="n">
         <v>0.837</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" s="0" t="n">
         <v>0.0200420618057251</v>
       </c>
       <c r="E3" s="0">
@@ -19026,7 +19026,7 @@
       <c r="C4" s="0" t="n">
         <v>0.828</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="0" t="n">
         <v>0.0202435664832592</v>
       </c>
       <c r="E4" s="0">
@@ -19082,7 +19082,7 @@
       <c r="C5" s="0" t="n">
         <v>0.8179999999999999</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="0" t="n">
         <v>0.01856775023043156</v>
       </c>
       <c r="E5" s="0">
@@ -19138,7 +19138,7 @@
       <c r="C6" s="0" t="n">
         <v>0.8110000000000001</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="0" t="n">
         <v>0.02292344346642494</v>
       </c>
       <c r="E6" s="0">
@@ -19194,7 +19194,7 @@
       <c r="C7" s="0" t="n">
         <v>0.803</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="0" t="n">
         <v>0.02005913108587265</v>
       </c>
       <c r="E7" s="0">
@@ -19250,7 +19250,7 @@
       <c r="C8" s="0" t="n">
         <v>0.797</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="0" t="n">
         <v>0.02002382278442383</v>
       </c>
       <c r="E8" s="0">
@@ -19306,7 +19306,7 @@
       <c r="C9" s="0" t="n">
         <v>0.791</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="0" t="n">
         <v>0.02062098495662212</v>
       </c>
       <c r="E9" s="0">
@@ -19362,7 +19362,7 @@
       <c r="C10" s="0" t="n">
         <v>0.785</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="0" t="n">
         <v>0.02150164172053337</v>
       </c>
       <c r="E10" s="0">
@@ -19418,7 +19418,7 @@
       <c r="C11" s="0" t="n">
         <v>0.779</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" s="0" t="n">
         <v>0.02074512094259262</v>
       </c>
       <c r="E11" s="0">
@@ -19474,7 +19474,7 @@
       <c r="C12" s="0" t="n">
         <v>0.774</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" s="0" t="n">
         <v>0.02223155833780766</v>
       </c>
       <c r="E12" s="0">
@@ -19530,7 +19530,7 @@
       <c r="C13" s="0" t="n">
         <v>0.768</v>
       </c>
-      <c r="D13" t="n">
+      <c r="D13" s="0" t="n">
         <v>0.02061885595321655</v>
       </c>
       <c r="E13" s="0">
@@ -19586,7 +19586,7 @@
       <c r="C14" s="0" t="n">
         <v>0.764</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D14" s="0" t="n">
         <v>0.02157804369926453</v>
       </c>
       <c r="E14" s="0">
@@ -19642,7 +19642,7 @@
       <c r="C15" s="0" t="n">
         <v>0.759</v>
       </c>
-      <c r="D15" t="n">
+      <c r="D15" s="0" t="n">
         <v>0.02084491401910782</v>
       </c>
       <c r="E15" s="0">
@@ -19698,7 +19698,7 @@
       <c r="C16" s="0" t="n">
         <v>0.754</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D16" s="0" t="n">
         <v>0.02178681455552578</v>
       </c>
       <c r="E16" s="0">
@@ -19754,7 +19754,7 @@
       <c r="C17" s="0" t="n">
         <v>0.75</v>
       </c>
-      <c r="D17" t="n">
+      <c r="D17" s="0" t="n">
         <v>0.02149804309010506</v>
       </c>
       <c r="E17" s="0">
@@ -19810,7 +19810,7 @@
       <c r="C18" s="0" t="n">
         <v>0.746</v>
       </c>
-      <c r="D18" t="n">
+      <c r="D18" s="0" t="n">
         <v>0.02160311862826347</v>
       </c>
       <c r="E18" s="0">
@@ -19866,7 +19866,7 @@
       <c r="C19" s="0" t="n">
         <v>0.742</v>
       </c>
-      <c r="D19" t="n">
+      <c r="D19" s="0" t="n">
         <v>0.02212035283446312</v>
       </c>
       <c r="E19" s="0">
@@ -19922,7 +19922,7 @@
       <c r="C20" s="0" t="n">
         <v>0.737</v>
       </c>
-      <c r="D20" t="n">
+      <c r="D20" s="0" t="n">
         <v>0.02196707017719746</v>
       </c>
       <c r="E20" s="0">
@@ -19978,7 +19978,7 @@
       <c r="C21" s="0" t="n">
         <v>0.733</v>
       </c>
-      <c r="D21" t="n">
+      <c r="D21" s="0" t="n">
         <v>0.02210067585110664</v>
       </c>
       <c r="E21" s="0">
@@ -20034,7 +20034,7 @@
       <c r="C22" s="0" t="n">
         <v>0.729</v>
       </c>
-      <c r="D22" t="n">
+      <c r="D22" s="0" t="n">
         <v>0.02124469913542271</v>
       </c>
       <c r="E22" s="0">
@@ -20090,7 +20090,7 @@
       <c r="C23" s="0" t="n">
         <v>0.726</v>
       </c>
-      <c r="D23" t="n">
+      <c r="D23" s="0" t="n">
         <v>0.02223465405404568</v>
       </c>
       <c r="E23" s="0">
@@ -20146,7 +20146,7 @@
       <c r="C24" s="0" t="n">
         <v>0.722</v>
       </c>
-      <c r="D24" t="n">
+      <c r="D24" s="0" t="n">
         <v>0.02199913933873177</v>
       </c>
       <c r="E24" s="0">
@@ -20202,7 +20202,7 @@
       <c r="C25" s="0" t="n">
         <v>0.718</v>
       </c>
-      <c r="D25" t="n">
+      <c r="D25" s="0" t="n">
         <v>0.0226028598845005</v>
       </c>
       <c r="E25" s="0">
@@ -20258,7 +20258,7 @@
       <c r="C26" s="0" t="n">
         <v>0.714</v>
       </c>
-      <c r="D26" t="n">
+      <c r="D26" s="0" t="n">
         <v>0.02136674337089062</v>
       </c>
       <c r="E26" s="0">
@@ -20314,7 +20314,7 @@
       <c r="C27" s="0" t="n">
         <v>0.711</v>
       </c>
-      <c r="D27" t="n">
+      <c r="D27" s="0" t="n">
         <v>0.02244500815868378</v>
       </c>
       <c r="E27" s="0">
@@ -20370,7 +20370,7 @@
       <c r="C28" s="0" t="n">
         <v>0.707</v>
       </c>
-      <c r="D28" t="n">
+      <c r="D28" s="0" t="n">
         <v>0.02068980224430561</v>
       </c>
       <c r="E28" s="0">
@@ -20426,7 +20426,7 @@
       <c r="C29" s="0" t="n">
         <v>0.704</v>
       </c>
-      <c r="D29" t="n">
+      <c r="D29" s="0" t="n">
         <v>0.0218848567456007</v>
       </c>
       <c r="E29" s="0">
@@ -20482,7 +20482,7 @@
       <c r="C30" s="0" t="n">
         <v>0.701</v>
       </c>
-      <c r="D30" t="n">
+      <c r="D30" s="0" t="n">
         <v>0.02142326533794403</v>
       </c>
       <c r="E30" s="0">
@@ -20538,7 +20538,7 @@
       <c r="C31" s="0" t="n">
         <v>0.697</v>
       </c>
-      <c r="D31" t="n">
+      <c r="D31" s="0" t="n">
         <v>0.02206030488014221</v>
       </c>
       <c r="E31" s="0">
@@ -20594,7 +20594,7 @@
       <c r="C32" s="0" t="n">
         <v>0.694</v>
       </c>
-      <c r="D32" t="n">
+      <c r="D32" s="0" t="n">
         <v>0.02066031657159328</v>
       </c>
       <c r="E32" s="0">
@@ -20650,7 +20650,7 @@
       <c r="C33" s="0" t="n">
         <v>0.6909999999999999</v>
       </c>
-      <c r="D33" t="n">
+      <c r="D33" s="0" t="n">
         <v>0.02202636934816837</v>
       </c>
       <c r="E33" s="0">
@@ -20706,7 +20706,7 @@
       <c r="C34" s="0" t="n">
         <v>0.6870000000000001</v>
       </c>
-      <c r="D34" t="n">
+      <c r="D34" s="0" t="n">
         <v>0.02086247317492962</v>
       </c>
       <c r="E34" s="0">
@@ -20762,7 +20762,7 @@
       <c r="C35" s="0" t="n">
         <v>0.6840000000000001</v>
       </c>
-      <c r="D35" t="n">
+      <c r="D35" s="0" t="n">
         <v>0.02169629000127316</v>
       </c>
       <c r="E35" s="0">
@@ -20818,7 +20818,7 @@
       <c r="C36" s="0" t="n">
         <v>0.681</v>
       </c>
-      <c r="D36" t="n">
+      <c r="D36" s="0" t="n">
         <v>0.02072627283632755</v>
       </c>
       <c r="E36" s="0">
@@ -20874,7 +20874,7 @@
       <c r="C37" s="0" t="n">
         <v>0.678</v>
       </c>
-      <c r="D37" t="n">
+      <c r="D37" s="0" t="n">
         <v>0.02208458632230759</v>
       </c>
       <c r="E37" s="0">
@@ -20930,7 +20930,7 @@
       <c r="C38" s="0" t="n">
         <v>0.675</v>
       </c>
-      <c r="D38" t="n">
+      <c r="D38" s="0" t="n">
         <v>0.02080466970801353</v>
       </c>
       <c r="E38" s="0">
@@ -20986,7 +20986,7 @@
       <c r="C39" s="0" t="n">
         <v>0.672</v>
       </c>
-      <c r="D39" t="n">
+      <c r="D39" s="0" t="n">
         <v>0.02198246121406555</v>
       </c>
       <c r="E39" s="0">
@@ -21042,7 +21042,7 @@
       <c r="C40" s="0" t="n">
         <v>0.669</v>
       </c>
-      <c r="D40" t="n">
+      <c r="D40" s="0" t="n">
         <v>0.0207621343433857</v>
       </c>
       <c r="E40" s="0">
@@ -21098,7 +21098,7 @@
       <c r="C41" s="0" t="n">
         <v>0.666</v>
       </c>
-      <c r="D41" t="n">
+      <c r="D41" s="0" t="n">
         <v>0.02174874022603035</v>
       </c>
       <c r="E41" s="0">
@@ -21154,7 +21154,7 @@
       <c r="C42" s="0" t="n">
         <v>0.663</v>
       </c>
-      <c r="D42" t="n">
+      <c r="D42" s="0" t="n">
         <v>0.02079889923334122</v>
       </c>
       <c r="E42" s="0">
@@ -21210,7 +21210,7 @@
       <c r="C43" s="0" t="n">
         <v>0.66</v>
       </c>
-      <c r="D43" t="n">
+      <c r="D43" s="0" t="n">
         <v>0.02128463797271252</v>
       </c>
       <c r="E43" s="0">
@@ -21266,7 +21266,7 @@
       <c r="C44" s="0" t="n">
         <v>0.657</v>
       </c>
-      <c r="D44" t="n">
+      <c r="D44" s="0" t="n">
         <v>0.02105836756527424</v>
       </c>
       <c r="E44" s="0">
@@ -21322,7 +21322,7 @@
       <c r="C45" s="0" t="n">
         <v>0.654</v>
       </c>
-      <c r="D45" t="n">
+      <c r="D45" s="0" t="n">
         <v>0.02128434740006924</v>
       </c>
       <c r="E45" s="0">
@@ -21378,7 +21378,7 @@
       <c r="C46" s="0" t="n">
         <v>0.651</v>
       </c>
-      <c r="D46" t="n">
+      <c r="D46" s="0" t="n">
         <v>0.02171558514237404</v>
       </c>
       <c r="E46" s="0">
@@ -21434,7 +21434,7 @@
       <c r="C47" s="0" t="n">
         <v>0.648</v>
       </c>
-      <c r="D47" t="n">
+      <c r="D47" s="0" t="n">
         <v>0.02162325009703636</v>
       </c>
       <c r="E47" s="0">
@@ -21490,7 +21490,7 @@
       <c r="C48" s="0" t="n">
         <v>0.646</v>
       </c>
-      <c r="D48" t="n">
+      <c r="D48" s="0" t="n">
         <v>0.02090091444551945</v>
       </c>
       <c r="E48" s="0">
@@ -21546,7 +21546,7 @@
       <c r="C49" s="0" t="n">
         <v>0.643</v>
       </c>
-      <c r="D49" t="n">
+      <c r="D49" s="0" t="n">
         <v>0.02139896526932716</v>
       </c>
       <c r="E49" s="0">
@@ -21602,7 +21602,7 @@
       <c r="C50" s="0" t="n">
         <v>0.64</v>
       </c>
-      <c r="D50" t="n">
+      <c r="D50" s="0" t="n">
         <v>0.02111426182091236</v>
       </c>
       <c r="E50" s="0">
@@ -21658,7 +21658,7 @@
       <c r="C51" s="0" t="n">
         <v>0.637</v>
       </c>
-      <c r="D51" t="n">
+      <c r="D51" s="0" t="n">
         <v>0.02089146338403225</v>
       </c>
       <c r="E51" s="0">
@@ -21714,7 +21714,7 @@
       <c r="C52" s="0" t="n">
         <v>0.634</v>
       </c>
-      <c r="D52" t="n">
+      <c r="D52" s="0" t="n">
         <v>0.02088642492890358</v>
       </c>
       <c r="E52" s="0">
@@ -21770,7 +21770,7 @@
       <c r="C53" s="0" t="n">
         <v>0.631</v>
       </c>
-      <c r="D53" t="n">
+      <c r="D53" s="0" t="n">
         <v>0.02163968607783318</v>
       </c>
       <c r="E53" s="0">
@@ -21826,7 +21826,7 @@
       <c r="C54" s="0" t="n">
         <v>0.629</v>
       </c>
-      <c r="D54" t="n">
+      <c r="D54" s="0" t="n">
         <v>0.0208536833524704</v>
       </c>
       <c r="E54" s="0">
@@ -21882,7 +21882,7 @@
       <c r="C55" s="0" t="n">
         <v>0.626</v>
       </c>
-      <c r="D55" t="n">
+      <c r="D55" s="0" t="n">
         <v>0.02042403817176819</v>
       </c>
       <c r="E55" s="0">
@@ -21938,7 +21938,7 @@
       <c r="C56" s="0" t="n">
         <v>0.623</v>
       </c>
-      <c r="D56" t="n">
+      <c r="D56" s="0" t="n">
         <v>0.02127382904291153</v>
       </c>
       <c r="E56" s="0">
@@ -21994,7 +21994,7 @@
       <c r="C57" s="0" t="n">
         <v>0.621</v>
       </c>
-      <c r="D57" t="n">
+      <c r="D57" s="0" t="n">
         <v>0.02156965248286724</v>
       </c>
       <c r="E57" s="0">
@@ -22050,7 +22050,7 @@
       <c r="C58" s="0" t="n">
         <v>0.618</v>
       </c>
-      <c r="D58" t="n">
+      <c r="D58" s="0" t="n">
         <v>0.0206918828189373</v>
       </c>
       <c r="E58" s="0">
@@ -22106,7 +22106,7 @@
       <c r="C59" s="0" t="n">
         <v>0.615</v>
       </c>
-      <c r="D59" t="n">
+      <c r="D59" s="0" t="n">
         <v>0.02107076346874237</v>
       </c>
       <c r="E59" s="0">
@@ -22162,7 +22162,7 @@
       <c r="C60" s="0" t="n">
         <v>0.613</v>
       </c>
-      <c r="D60" t="n">
+      <c r="D60" s="0" t="n">
         <v>0.02087909355759621</v>
       </c>
       <c r="E60" s="0">
@@ -22218,7 +22218,7 @@
       <c r="C61" s="0" t="n">
         <v>0.61</v>
       </c>
-      <c r="D61" t="n">
+      <c r="D61" s="0" t="n">
         <v>0.02139941975474358</v>
       </c>
       <c r="E61" s="0">
@@ -22274,7 +22274,7 @@
       <c r="C62" s="0" t="n">
         <v>0.608</v>
       </c>
-      <c r="D62" t="n">
+      <c r="D62" s="0" t="n">
         <v>0.02168705686926842</v>
       </c>
       <c r="E62" s="0">
@@ -22330,7 +22330,7 @@
       <c r="C63" s="0" t="n">
         <v>0.605</v>
       </c>
-      <c r="D63" t="n">
+      <c r="D63" s="0" t="n">
         <v>0.02088871784508228</v>
       </c>
       <c r="E63" s="0">
@@ -22386,7 +22386,7 @@
       <c r="C64" s="0" t="n">
         <v>0.603</v>
       </c>
-      <c r="D64" t="n">
+      <c r="D64" s="0" t="n">
         <v>0.02038130722939968</v>
       </c>
       <c r="E64" s="0">
@@ -22442,7 +22442,7 @@
       <c r="C65" s="0" t="n">
         <v>0.6</v>
       </c>
-      <c r="D65" t="n">
+      <c r="D65" s="0" t="n">
         <v>0.02090147696435452</v>
       </c>
       <c r="E65" s="0">
@@ -22498,7 +22498,7 @@
       <c r="C66" s="0" t="n">
         <v>0.597</v>
       </c>
-      <c r="D66" t="n">
+      <c r="D66" s="0" t="n">
         <v>0.02089935913681984</v>
       </c>
       <c r="E66" s="0">
@@ -22554,7 +22554,7 @@
       <c r="C67" s="0" t="n">
         <v>0.595</v>
       </c>
-      <c r="D67" t="n">
+      <c r="D67" s="0" t="n">
         <v>0.02123693376779556</v>
       </c>
       <c r="E67" s="0">
@@ -22610,7 +22610,7 @@
       <c r="C68" s="0" t="n">
         <v>0.592</v>
       </c>
-      <c r="D68" t="n">
+      <c r="D68" s="0" t="n">
         <v>0.02121633850038052</v>
       </c>
       <c r="E68" s="0">
@@ -22666,7 +22666,7 @@
       <c r="C69" s="0" t="n">
         <v>0.59</v>
       </c>
-      <c r="D69" t="n">
+      <c r="D69" s="0" t="n">
         <v>0.02192088775336742</v>
       </c>
       <c r="E69" s="0">
@@ -22722,7 +22722,7 @@
       <c r="C70" s="0" t="n">
         <v>0.587</v>
       </c>
-      <c r="D70" t="n">
+      <c r="D70" s="0" t="n">
         <v>0.02134180627763271</v>
       </c>
       <c r="E70" s="0">
@@ -22778,7 +22778,7 @@
       <c r="C71" s="0" t="n">
         <v>0.585</v>
       </c>
-      <c r="D71" t="n">
+      <c r="D71" s="0" t="n">
         <v>0.02118257060647011</v>
       </c>
       <c r="E71" s="0">
@@ -22834,7 +22834,7 @@
       <c r="C72" s="0" t="n">
         <v>0.582</v>
       </c>
-      <c r="D72" t="n">
+      <c r="D72" s="0" t="n">
         <v>0.02070923149585724</v>
       </c>
       <c r="E72" s="0">
@@ -22890,7 +22890,7 @@
       <c r="C73" s="0" t="n">
         <v>0.58</v>
       </c>
-      <c r="D73" t="n">
+      <c r="D73" s="0" t="n">
         <v>0.02084982767701149</v>
       </c>
       <c r="E73" s="0">
@@ -22946,7 +22946,7 @@
       <c r="C74" s="0" t="n">
         <v>0.578</v>
       </c>
-      <c r="D74" t="n">
+      <c r="D74" s="0" t="n">
         <v>0.02178002707660198</v>
       </c>
       <c r="E74" s="0">
@@ -23002,7 +23002,7 @@
       <c r="C75" s="0" t="n">
         <v>0.575</v>
       </c>
-      <c r="D75" t="n">
+      <c r="D75" s="0" t="n">
         <v>0.0216306746006012</v>
       </c>
       <c r="E75" s="0">
@@ -23058,7 +23058,7 @@
       <c r="C76" s="0" t="n">
         <v>0.573</v>
       </c>
-      <c r="D76" t="n">
+      <c r="D76" s="0" t="n">
         <v>0.0215228870511055</v>
       </c>
       <c r="E76" s="0">
@@ -23114,7 +23114,7 @@
       <c r="C77" s="0" t="n">
         <v>0.57</v>
       </c>
-      <c r="D77" t="n">
+      <c r="D77" s="0" t="n">
         <v>0.02099636942148209</v>
       </c>
       <c r="E77" s="0">
@@ -23170,7 +23170,7 @@
       <c r="C78" s="0" t="n">
         <v>0.5679999999999999</v>
       </c>
-      <c r="D78" t="n">
+      <c r="D78" s="0" t="n">
         <v>0.02120652794837952</v>
       </c>
       <c r="E78" s="0">
@@ -23226,7 +23226,7 @@
       <c r="C79" s="0" t="n">
         <v>0.5649999999999999</v>
       </c>
-      <c r="D79" t="n">
+      <c r="D79" s="0" t="n">
         <v>0.02128704264760017</v>
       </c>
       <c r="E79" s="0">
@@ -23282,7 +23282,7 @@
       <c r="C80" s="0" t="n">
         <v>0.5629999999999999</v>
       </c>
-      <c r="D80" t="n">
+      <c r="D80" s="0" t="n">
         <v>0.0215698704123497</v>
       </c>
       <c r="E80" s="0">
@@ -23338,7 +23338,7 @@
       <c r="C81" s="0" t="n">
         <v>0.5610000000000001</v>
       </c>
-      <c r="D81" t="n">
+      <c r="D81" s="0" t="n">
         <v>0.02135146409273148</v>
       </c>
       <c r="E81" s="0">
@@ -23394,7 +23394,7 @@
       <c r="C82" s="0" t="n">
         <v>0.5580000000000001</v>
       </c>
-      <c r="D82" t="n">
+      <c r="D82" s="0" t="n">
         <v>0.02219929546117783</v>
       </c>
       <c r="E82" s="0">
@@ -23450,7 +23450,7 @@
       <c r="C83" s="0" t="n">
         <v>0.556</v>
       </c>
-      <c r="D83" t="n">
+      <c r="D83" s="0" t="n">
         <v>0.02134930714964867</v>
       </c>
       <c r="E83" s="0">
@@ -23506,7 +23506,7 @@
       <c r="C84" s="0" t="n">
         <v>0.554</v>
       </c>
-      <c r="D84" t="n">
+      <c r="D84" s="0" t="n">
         <v>0.0212129782885313</v>
       </c>
       <c r="E84" s="0">
@@ -23562,7 +23562,7 @@
       <c r="C85" s="0" t="n">
         <v>0.551</v>
       </c>
-      <c r="D85" t="n">
+      <c r="D85" s="0" t="n">
         <v>0.02233623340725899</v>
       </c>
       <c r="E85" s="0">
@@ -23618,7 +23618,7 @@
       <c r="C86" s="0" t="n">
         <v>0.549</v>
       </c>
-      <c r="D86" t="n">
+      <c r="D86" s="0" t="n">
         <v>0.0209533553570509</v>
       </c>
       <c r="E86" s="0">
@@ -23674,7 +23674,7 @@
       <c r="C87" s="0" t="n">
         <v>0.546</v>
       </c>
-      <c r="D87" t="n">
+      <c r="D87" s="0" t="n">
         <v>0.02204925194382668</v>
       </c>
       <c r="E87" s="0">
@@ -23730,7 +23730,7 @@
       <c r="C88" s="0" t="n">
         <v>0.544</v>
       </c>
-      <c r="D88" t="n">
+      <c r="D88" s="0" t="n">
         <v>0.02171573415398598</v>
       </c>
       <c r="E88" s="0">
@@ -23786,7 +23786,7 @@
       <c r="C89" s="0" t="n">
         <v>0.542</v>
       </c>
-      <c r="D89" t="n">
+      <c r="D89" s="0" t="n">
         <v>0.0216961745172739</v>
       </c>
       <c r="E89" s="0">
@@ -23842,7 +23842,7 @@
       <c r="C90" s="0" t="n">
         <v>0.539</v>
       </c>
-      <c r="D90" t="n">
+      <c r="D90" s="0" t="n">
         <v>0.02190676517784595</v>
       </c>
       <c r="E90" s="0">
@@ -23898,7 +23898,7 @@
       <c r="C91" s="0" t="n">
         <v>0.537</v>
       </c>
-      <c r="D91" t="n">
+      <c r="D91" s="0" t="n">
         <v>0.02175609022378922</v>
       </c>
       <c r="E91" s="0">
@@ -23954,7 +23954,7 @@
       <c r="C92" s="0" t="n">
         <v>0.534</v>
       </c>
-      <c r="D92" t="n">
+      <c r="D92" s="0" t="n">
         <v>0.02242948859930038</v>
       </c>
       <c r="E92" s="0">
@@ -24010,7 +24010,7 @@
       <c r="C93" s="0" t="n">
         <v>0.533</v>
       </c>
-      <c r="D93" t="n">
+      <c r="D93" s="0" t="n">
         <v>0.0215414147824049</v>
       </c>
       <c r="E93" s="0">
@@ -24066,7 +24066,7 @@
       <c r="C94" s="0" t="n">
         <v>0.53</v>
       </c>
-      <c r="D94" t="n">
+      <c r="D94" s="0" t="n">
         <v>0.02252337895333767</v>
       </c>
       <c r="E94" s="0">
@@ -24122,7 +24122,7 @@
       <c r="C95" s="0" t="n">
         <v>0.528</v>
       </c>
-      <c r="D95" t="n">
+      <c r="D95" s="0" t="n">
         <v>0.02160502783954144</v>
       </c>
       <c r="E95" s="0">
@@ -24171,7 +24171,7 @@
       <c r="C96" s="0" t="n">
         <v>0.526</v>
       </c>
-      <c r="D96" t="n">
+      <c r="D96" s="0" t="n">
         <v>0.02235906384885311</v>
       </c>
       <c r="E96" s="0">
@@ -24220,7 +24220,7 @@
       <c r="C97" s="0" t="n">
         <v>0.524</v>
       </c>
-      <c r="D97" t="n">
+      <c r="D97" s="0" t="n">
         <v>0.0217084027826786</v>
       </c>
       <c r="E97" s="0">
@@ -24269,7 +24269,7 @@
       <c r="C98" s="0" t="n">
         <v>0.521</v>
       </c>
-      <c r="D98" t="n">
+      <c r="D98" s="0" t="n">
         <v>0.02225402183830738</v>
       </c>
       <c r="E98" s="0">
@@ -24318,7 +24318,7 @@
       <c r="C99" s="0" t="n">
         <v>0.519</v>
       </c>
-      <c r="D99" t="n">
+      <c r="D99" s="0" t="n">
         <v>0.02203675732016563</v>
       </c>
       <c r="E99" s="0">
@@ -24367,7 +24367,7 @@
       <c r="C100" s="0" t="n">
         <v>0.517</v>
       </c>
-      <c r="D100" t="n">
+      <c r="D100" s="0" t="n">
         <v>0.02238716930150986</v>
       </c>
       <c r="E100" s="0">
@@ -24416,7 +24416,7 @@
       <c r="C101" s="0" t="n">
         <v>0.514</v>
       </c>
-      <c r="D101" t="n">
+      <c r="D101" s="0" t="n">
         <v>0.02200327999889851</v>
       </c>
       <c r="E101" s="0">
@@ -24465,7 +24465,7 @@
       <c r="C102" s="0" t="n">
         <v>0.512</v>
       </c>
-      <c r="D102" t="n">
+      <c r="D102" s="0" t="n">
         <v>0.02229078486561775</v>
       </c>
       <c r="E102" s="0">
@@ -24514,7 +24514,7 @@
       <c r="C103" s="0" t="n">
         <v>0.51</v>
       </c>
-      <c r="D103" t="n">
+      <c r="D103" s="0" t="n">
         <v>0.02204912714660168</v>
       </c>
       <c r="E103" s="0">
@@ -24563,7 +24563,7 @@
       <c r="C104" s="0" t="n">
         <v>0.508</v>
       </c>
-      <c r="D104" t="n">
+      <c r="D104" s="0" t="n">
         <v>0.02202761545777321</v>
       </c>
       <c r="E104" s="0">
@@ -24612,7 +24612,7 @@
       <c r="C105" s="0" t="n">
         <v>0.506</v>
       </c>
-      <c r="D105" t="n">
+      <c r="D105" s="0" t="n">
         <v>0.02176796086132526</v>
       </c>
       <c r="E105" s="0">
@@ -24661,7 +24661,7 @@
       <c r="C106" s="0" t="n">
         <v>0.503</v>
       </c>
-      <c r="D106" t="n">
+      <c r="D106" s="0" t="n">
         <v>0.02218662574887276</v>
       </c>
       <c r="E106" s="0">
@@ -24710,7 +24710,7 @@
       <c r="C107" s="0" t="n">
         <v>0.501</v>
       </c>
-      <c r="D107" t="n">
+      <c r="D107" s="0" t="n">
         <v>0.02234361320734024</v>
       </c>
       <c r="E107" s="0">
@@ -24759,7 +24759,7 @@
       <c r="C108" s="0" t="n">
         <v>0.499</v>
       </c>
-      <c r="D108" t="n">
+      <c r="D108" s="0" t="n">
         <v>0.02194085530936718</v>
       </c>
       <c r="E108" s="0">
@@ -24808,7 +24808,7 @@
       <c r="C109" s="0" t="n">
         <v>0.496</v>
       </c>
-      <c r="D109" t="n">
+      <c r="D109" s="0" t="n">
         <v>0.02266308106482029</v>
       </c>
       <c r="E109" s="0">
@@ -24857,7 +24857,7 @@
       <c r="C110" s="0" t="n">
         <v>0.494</v>
       </c>
-      <c r="D110" t="n">
+      <c r="D110" s="0" t="n">
         <v>0.02264226041734219</v>
       </c>
       <c r="E110" s="0">
@@ -24906,7 +24906,7 @@
       <c r="C111" s="0" t="n">
         <v>0.492</v>
       </c>
-      <c r="D111" t="n">
+      <c r="D111" s="0" t="n">
         <v>0.02145604602992535</v>
       </c>
       <c r="E111" s="0">
@@ -24955,7 +24955,7 @@
       <c r="C112" s="0" t="n">
         <v>0.49</v>
       </c>
-      <c r="D112" t="n">
+      <c r="D112" s="0" t="n">
         <v>0.02272169478237629</v>
       </c>
       <c r="E112" s="0">
@@ -25004,7 +25004,7 @@
       <c r="C113" s="0" t="n">
         <v>0.488</v>
       </c>
-      <c r="D113" t="n">
+      <c r="D113" s="0" t="n">
         <v>0.02283627167344093</v>
       </c>
       <c r="E113" s="0">
@@ -25053,7 +25053,7 @@
       <c r="C114" s="0" t="n">
         <v>0.485</v>
       </c>
-      <c r="D114" t="n">
+      <c r="D114" s="0" t="n">
         <v>0.02256097830832005</v>
       </c>
       <c r="E114" s="0">
@@ -25102,7 +25102,7 @@
       <c r="C115" s="0" t="n">
         <v>0.483</v>
       </c>
-      <c r="D115" t="n">
+      <c r="D115" s="0" t="n">
         <v>0.02283190004527569</v>
       </c>
       <c r="E115" s="0">
@@ -25151,7 +25151,7 @@
       <c r="C116" s="0" t="n">
         <v>0.481</v>
       </c>
-      <c r="D116" t="n">
+      <c r="D116" s="0" t="n">
         <v>0.02224512957036495</v>
       </c>
       <c r="E116" s="0">
@@ -25200,7 +25200,7 @@
       <c r="C117" s="0" t="n">
         <v>0.479</v>
       </c>
-      <c r="D117" t="n">
+      <c r="D117" s="0" t="n">
         <v>0.02277129143476486</v>
       </c>
       <c r="E117" s="0">
@@ -25249,7 +25249,7 @@
       <c r="C118" s="0" t="n">
         <v>0.477</v>
       </c>
-      <c r="D118" t="n">
+      <c r="D118" s="0" t="n">
         <v>0.02282169088721275</v>
       </c>
       <c r="E118" s="0">
@@ -25298,7 +25298,7 @@
       <c r="C119" s="0" t="n">
         <v>0.474</v>
       </c>
-      <c r="D119" t="n">
+      <c r="D119" s="0" t="n">
         <v>0.02233251929283142</v>
       </c>
       <c r="E119" s="0">
@@ -25347,7 +25347,7 @@
       <c r="C120" s="0" t="n">
         <v>0.473</v>
       </c>
-      <c r="D120" t="n">
+      <c r="D120" s="0" t="n">
         <v>0.02308384887874126</v>
       </c>
       <c r="E120" s="0">
@@ -25396,7 +25396,7 @@
       <c r="C121" s="0" t="n">
         <v>0.47</v>
       </c>
-      <c r="D121" t="n">
+      <c r="D121" s="0" t="n">
         <v>0.02248584665358067</v>
       </c>
       <c r="E121" s="0">
@@ -25445,7 +25445,7 @@
       <c r="C122" s="0" t="n">
         <v>0.468</v>
       </c>
-      <c r="D122" t="n">
+      <c r="D122" s="0" t="n">
         <v>0.02315918728709221</v>
       </c>
       <c r="E122" s="0">
@@ -25494,7 +25494,7 @@
       <c r="C123" s="0" t="n">
         <v>0.466</v>
       </c>
-      <c r="D123" t="n">
+      <c r="D123" s="0" t="n">
         <v>0.02308138087391853</v>
       </c>
       <c r="E123" s="0">
@@ -25543,7 +25543,7 @@
       <c r="C124" s="0" t="n">
         <v>0.464</v>
       </c>
-      <c r="D124" t="n">
+      <c r="D124" s="0" t="n">
         <v>0.02228741347789764</v>
       </c>
       <c r="E124" s="0">
@@ -25592,7 +25592,7 @@
       <c r="C125" s="0" t="n">
         <v>0.462</v>
       </c>
-      <c r="D125" t="n">
+      <c r="D125" s="0" t="n">
         <v>0.02303110808134079</v>
       </c>
       <c r="E125" s="0">
@@ -25641,7 +25641,7 @@
       <c r="C126" s="0" t="n">
         <v>0.46</v>
       </c>
-      <c r="D126" t="n">
+      <c r="D126" s="0" t="n">
         <v>0.02348831482231617</v>
       </c>
       <c r="E126" s="0">
@@ -25690,7 +25690,7 @@
       <c r="C127" s="0" t="n">
         <v>0.458</v>
       </c>
-      <c r="D127" t="n">
+      <c r="D127" s="0" t="n">
         <v>0.02262923307716846</v>
       </c>
       <c r="E127" s="0">
@@ -25739,7 +25739,7 @@
       <c r="C128" s="0" t="n">
         <v>0.455</v>
       </c>
-      <c r="D128" t="n">
+      <c r="D128" s="0" t="n">
         <v>0.02375646680593491</v>
       </c>
       <c r="E128" s="0">
@@ -25788,7 +25788,7 @@
       <c r="C129" s="0" t="n">
         <v>0.453</v>
       </c>
-      <c r="D129" t="n">
+      <c r="D129" s="0" t="n">
         <v>0.02298040315508842</v>
       </c>
       <c r="E129" s="0">
@@ -25837,7 +25837,7 @@
       <c r="C130" s="0" t="n">
         <v>0.451</v>
       </c>
-      <c r="D130" t="n">
+      <c r="D130" s="0" t="n">
         <v>0.0228426568210125</v>
       </c>
       <c r="E130" s="0">
@@ -25886,7 +25886,7 @@
       <c r="C131" s="0" t="n">
         <v>0.449</v>
       </c>
-      <c r="D131" t="n">
+      <c r="D131" s="0" t="n">
         <v>0.02334821410477161</v>
       </c>
       <c r="E131" s="0">
@@ -25935,7 +25935,7 @@
       <c r="C132" s="0" t="n">
         <v>0.447</v>
       </c>
-      <c r="D132" t="n">
+      <c r="D132" s="0" t="n">
         <v>0.02255835197865963</v>
       </c>
       <c r="E132" s="0">
@@ -25984,7 +25984,7 @@
       <c r="C133" s="0" t="n">
         <v>0.445</v>
       </c>
-      <c r="D133" t="n">
+      <c r="D133" s="0" t="n">
         <v>0.02312240190804005</v>
       </c>
       <c r="E133" s="0">
@@ -26033,7 +26033,7 @@
       <c r="C134" s="0" t="n">
         <v>0.443</v>
       </c>
-      <c r="D134" t="n">
+      <c r="D134" s="0" t="n">
         <v>0.02291266620159149</v>
       </c>
       <c r="E134" s="0">
@@ -26082,7 +26082,7 @@
       <c r="C135" s="0" t="n">
         <v>0.441</v>
       </c>
-      <c r="D135" t="n">
+      <c r="D135" s="0" t="n">
         <v>0.023176034912467</v>
       </c>
       <c r="E135" s="0">
@@ -26131,7 +26131,7 @@
       <c r="C136" s="0" t="n">
         <v>0.439</v>
       </c>
-      <c r="D136" t="n">
+      <c r="D136" s="0" t="n">
         <v>0.02292532101273537</v>
       </c>
       <c r="E136" s="0">
@@ -26180,7 +26180,7 @@
       <c r="C137" s="0" t="n">
         <v>0.437</v>
       </c>
-      <c r="D137" t="n">
+      <c r="D137" s="0" t="n">
         <v>0.02327945083379745</v>
       </c>
       <c r="E137" s="0">
@@ -26229,7 +26229,7 @@
       <c r="C138" s="0" t="n">
         <v>0.434</v>
       </c>
-      <c r="D138" t="n">
+      <c r="D138" s="0" t="n">
         <v>0.02313651889562607</v>
       </c>
       <c r="E138" s="0">
@@ -26278,7 +26278,7 @@
       <c r="C139" s="0" t="n">
         <v>0.432</v>
       </c>
-      <c r="D139" t="n">
+      <c r="D139" s="0" t="n">
         <v>0.02359609119594097</v>
       </c>
       <c r="E139" s="0">
@@ -26327,7 +26327,7 @@
       <c r="C140" s="0" t="n">
         <v>0.43</v>
       </c>
-      <c r="D140" t="n">
+      <c r="D140" s="0" t="n">
         <v>0.02316553890705109</v>
       </c>
       <c r="E140" s="0">
@@ -26376,7 +26376,7 @@
       <c r="C141" s="0" t="n">
         <v>0.428</v>
       </c>
-      <c r="D141" t="n">
+      <c r="D141" s="0" t="n">
         <v>0.02403800003230572</v>
       </c>
       <c r="E141" s="0">
@@ -26425,7 +26425,7 @@
       <c r="C142" s="0" t="n">
         <v>0.426</v>
       </c>
-      <c r="D142" t="n">
+      <c r="D142" s="0" t="n">
         <v>0.0228748694062233</v>
       </c>
       <c r="E142" s="0">
@@ -26474,7 +26474,7 @@
       <c r="C143" s="0" t="n">
         <v>0.424</v>
       </c>
-      <c r="D143" t="n">
+      <c r="D143" s="0" t="n">
         <v>0.02321753092110157</v>
       </c>
       <c r="E143" s="0">
@@ -26523,7 +26523,7 @@
       <c r="C144" s="0" t="n">
         <v>0.422</v>
       </c>
-      <c r="D144" t="n">
+      <c r="D144" s="0" t="n">
         <v>0.02334983088076115</v>
       </c>
       <c r="E144" s="0">
@@ -26572,7 +26572,7 @@
       <c r="C145" s="0" t="n">
         <v>0.42</v>
       </c>
-      <c r="D145" t="n">
+      <c r="D145" s="0" t="n">
         <v>0.02308961376547813</v>
       </c>
       <c r="E145" s="0">
@@ -26621,7 +26621,7 @@
       <c r="C146" s="0" t="n">
         <v>0.418</v>
       </c>
-      <c r="D146" t="n">
+      <c r="D146" s="0" t="n">
         <v>0.02444537356495857</v>
       </c>
       <c r="E146" s="0">
@@ -26670,7 +26670,7 @@
       <c r="C147" s="0" t="n">
         <v>0.416</v>
       </c>
-      <c r="D147" t="n">
+      <c r="D147" s="0" t="n">
         <v>0.02307135425508022</v>
       </c>
       <c r="E147" s="0">
@@ -26719,7 +26719,7 @@
       <c r="C148" s="0" t="n">
         <v>0.413</v>
       </c>
-      <c r="D148" t="n">
+      <c r="D148" s="0" t="n">
         <v>0.02379290014505386</v>
       </c>
       <c r="E148" s="0">
@@ -26768,7 +26768,7 @@
       <c r="C149" s="0" t="n">
         <v>0.411</v>
       </c>
-      <c r="D149" t="n">
+      <c r="D149" s="0" t="n">
         <v>0.02341685071587563</v>
       </c>
       <c r="E149" s="0">
@@ -26817,7 +26817,7 @@
       <c r="C150" s="0" t="n">
         <v>0.409</v>
       </c>
-      <c r="D150" t="n">
+      <c r="D150" s="0" t="n">
         <v>0.02343933098018169</v>
       </c>
       <c r="E150" s="0">
@@ -26866,7 +26866,7 @@
       <c r="C151" s="0" t="n">
         <v>0.407</v>
       </c>
-      <c r="D151" t="n">
+      <c r="D151" s="0" t="n">
         <v>0.02361765690147877</v>
       </c>
       <c r="E151" s="0">
@@ -26915,7 +26915,7 @@
       <c r="C152" s="0" t="n">
         <v>0.405</v>
       </c>
-      <c r="D152" t="n">
+      <c r="D152" s="0" t="n">
         <v>0.02412284165620804</v>
       </c>
       <c r="E152" s="0">
@@ -26964,7 +26964,7 @@
       <c r="C153" s="0" t="n">
         <v>0.403</v>
       </c>
-      <c r="D153" t="n">
+      <c r="D153" s="0" t="n">
         <v>0.02367998659610748</v>
       </c>
       <c r="E153" s="0">
@@ -27013,7 +27013,7 @@
       <c r="C154" s="0" t="n">
         <v>0.401</v>
       </c>
-      <c r="D154" t="n">
+      <c r="D154" s="0" t="n">
         <v>0.02378236874938011</v>
       </c>
       <c r="E154" s="0">
@@ -27062,7 +27062,7 @@
       <c r="C155" s="0" t="n">
         <v>0.399</v>
       </c>
-      <c r="D155" t="n">
+      <c r="D155" s="0" t="n">
         <v>0.02381190285086632</v>
       </c>
       <c r="E155" s="0">
@@ -27111,7 +27111,7 @@
       <c r="C156" s="0" t="n">
         <v>0.397</v>
       </c>
-      <c r="D156" t="n">
+      <c r="D156" s="0" t="n">
         <v>0.02335663884878159</v>
       </c>
       <c r="E156" s="0">
@@ -27160,7 +27160,7 @@
       <c r="C157" s="0" t="n">
         <v>0.395</v>
       </c>
-      <c r="D157" t="n">
+      <c r="D157" s="0" t="n">
         <v>0.02376625686883926</v>
       </c>
       <c r="E157" s="0">
@@ -27209,7 +27209,7 @@
       <c r="C158" s="0" t="n">
         <v>0.393</v>
       </c>
-      <c r="D158" t="n">
+      <c r="D158" s="0" t="n">
         <v>0.02348150312900543</v>
       </c>
       <c r="E158" s="0">
@@ -27258,7 +27258,7 @@
       <c r="C159" s="0" t="n">
         <v>0.39</v>
       </c>
-      <c r="D159" t="n">
+      <c r="D159" s="0" t="n">
         <v>0.02421257458627224</v>
       </c>
       <c r="E159" s="0">
@@ -27307,7 +27307,7 @@
       <c r="C160" s="0" t="n">
         <v>0.388</v>
       </c>
-      <c r="D160" t="n">
+      <c r="D160" s="0" t="n">
         <v>0.02338164113461971</v>
       </c>
       <c r="E160" s="0">
@@ -27356,7 +27356,7 @@
       <c r="C161" s="0" t="n">
         <v>0.386</v>
       </c>
-      <c r="D161" t="n">
+      <c r="D161" s="0" t="n">
         <v>0.02417968027293682</v>
       </c>
       <c r="E161" s="0">
@@ -27405,7 +27405,7 @@
       <c r="C162" s="0" t="n">
         <v>0.384</v>
       </c>
-      <c r="D162" t="n">
+      <c r="D162" s="0" t="n">
         <v>0.02359800599515438</v>
       </c>
       <c r="E162" s="0">
@@ -27454,7 +27454,7 @@
       <c r="C163" s="0" t="n">
         <v>0.382</v>
       </c>
-      <c r="D163" t="n">
+      <c r="D163" s="0" t="n">
         <v>0.02405710332095623</v>
       </c>
       <c r="E163" s="0">
@@ -27503,7 +27503,7 @@
       <c r="C164" s="0" t="n">
         <v>0.38</v>
       </c>
-      <c r="D164" t="n">
+      <c r="D164" s="0" t="n">
         <v>0.02362007275223732</v>
       </c>
       <c r="E164" s="0">
@@ -27552,7 +27552,7 @@
       <c r="C165" s="0" t="n">
         <v>0.378</v>
       </c>
-      <c r="D165" t="n">
+      <c r="D165" s="0" t="n">
         <v>0.02441132627427578</v>
       </c>
       <c r="E165" s="0">
@@ -27601,7 +27601,7 @@
       <c r="C166" s="0" t="n">
         <v>0.375</v>
       </c>
-      <c r="D166" t="n">
+      <c r="D166" s="0" t="n">
         <v>0.02377547696232796</v>
       </c>
       <c r="E166" s="0">
@@ -27650,7 +27650,7 @@
       <c r="C167" s="0" t="n">
         <v>0.373</v>
       </c>
-      <c r="D167" t="n">
+      <c r="D167" s="0" t="n">
         <v>0.02424614503979683</v>
       </c>
       <c r="E167" s="0">
@@ -27699,7 +27699,7 @@
       <c r="C168" s="0" t="n">
         <v>0.371</v>
       </c>
-      <c r="D168" t="n">
+      <c r="D168" s="0" t="n">
         <v>0.02394500561058521</v>
       </c>
       <c r="E168" s="0">
@@ -27748,7 +27748,7 @@
       <c r="C169" s="0" t="n">
         <v>0.369</v>
       </c>
-      <c r="D169" t="n">
+      <c r="D169" s="0" t="n">
         <v>0.02406875789165497</v>
       </c>
       <c r="E169" s="0">
@@ -27797,7 +27797,7 @@
       <c r="C170" s="0" t="n">
         <v>0.367</v>
       </c>
-      <c r="D170" t="n">
+      <c r="D170" s="0" t="n">
         <v>0.02440095134079456</v>
       </c>
       <c r="E170" s="0">
@@ -27846,7 +27846,7 @@
       <c r="C171" s="0" t="n">
         <v>0.365</v>
       </c>
-      <c r="D171" t="n">
+      <c r="D171" s="0" t="n">
         <v>0.02434027567505836</v>
       </c>
       <c r="E171" s="0">
@@ -27895,7 +27895,7 @@
       <c r="C172" s="0" t="n">
         <v>0.362</v>
       </c>
-      <c r="D172" t="n">
+      <c r="D172" s="0" t="n">
         <v>0.02376594208180904</v>
       </c>
       <c r="E172" s="0">
@@ -27944,7 +27944,7 @@
       <c r="C173" s="0" t="n">
         <v>0.361</v>
       </c>
-      <c r="D173" t="n">
+      <c r="D173" s="0" t="n">
         <v>0.02431243099272251</v>
       </c>
       <c r="E173" s="0">
@@ -27993,7 +27993,7 @@
       <c r="C174" s="0" t="n">
         <v>0.358</v>
       </c>
-      <c r="D174" t="n">
+      <c r="D174" s="0" t="n">
         <v>0.02424491569399834</v>
       </c>
       <c r="E174" s="0">
@@ -28042,7 +28042,7 @@
       <c r="C175" s="0" t="n">
         <v>0.356</v>
       </c>
-      <c r="D175" t="n">
+      <c r="D175" s="0" t="n">
         <v>0.02432944253087044</v>
       </c>
       <c r="E175" s="0">
@@ -28091,7 +28091,7 @@
       <c r="C176" s="0" t="n">
         <v>0.354</v>
       </c>
-      <c r="D176" t="n">
+      <c r="D176" s="0" t="n">
         <v>0.02473657205700874</v>
       </c>
       <c r="E176" s="0">
@@ -28140,7 +28140,7 @@
       <c r="C177" s="0" t="n">
         <v>0.352</v>
       </c>
-      <c r="D177" t="n">
+      <c r="D177" s="0" t="n">
         <v>0.02427547425031662</v>
       </c>
       <c r="E177" s="0">
@@ -28189,7 +28189,7 @@
       <c r="C178" s="0" t="n">
         <v>0.35</v>
       </c>
-      <c r="D178" t="n">
+      <c r="D178" s="0" t="n">
         <v>0.02418882772326469</v>
       </c>
       <c r="E178" s="0">
@@ -28238,7 +28238,7 @@
       <c r="C179" s="0" t="n">
         <v>0.348</v>
       </c>
-      <c r="D179" t="n">
+      <c r="D179" s="0" t="n">
         <v>0.0245915874838829</v>
       </c>
       <c r="E179" s="0">
@@ -28287,7 +28287,7 @@
       <c r="C180" s="0" t="n">
         <v>0.346</v>
       </c>
-      <c r="D180" t="n">
+      <c r="D180" s="0" t="n">
         <v>0.02487228251993656</v>
       </c>
       <c r="E180" s="0">
@@ -28336,7 +28336,7 @@
       <c r="C181" s="0" t="n">
         <v>0.343</v>
       </c>
-      <c r="D181" t="n">
+      <c r="D181" s="0" t="n">
         <v>0.02499474212527275</v>
       </c>
       <c r="E181" s="0">
@@ -28385,7 +28385,7 @@
       <c r="C182" s="0" t="n">
         <v>0.341</v>
       </c>
-      <c r="D182" t="n">
+      <c r="D182" s="0" t="n">
         <v>0.02505173347890377</v>
       </c>
       <c r="E182" s="0">
@@ -28434,7 +28434,7 @@
       <c r="C183" s="0" t="n">
         <v>0.339</v>
       </c>
-      <c r="D183" t="n">
+      <c r="D183" s="0" t="n">
         <v>0.02456580474972725</v>
       </c>
       <c r="E183" s="0">
@@ -28483,7 +28483,7 @@
       <c r="C184" s="0" t="n">
         <v>0.337</v>
       </c>
-      <c r="D184" t="n">
+      <c r="D184" s="0" t="n">
         <v>0.02429625019431114</v>
       </c>
       <c r="E184" s="0">
@@ -28532,7 +28532,7 @@
       <c r="C185" s="0" t="n">
         <v>0.335</v>
       </c>
-      <c r="D185" t="n">
+      <c r="D185" s="0" t="n">
         <v>0.02401648834347725</v>
       </c>
       <c r="E185" s="0">
@@ -28581,7 +28581,7 @@
       <c r="C186" s="0" t="n">
         <v>0.333</v>
       </c>
-      <c r="D186" t="n">
+      <c r="D186" s="0" t="n">
         <v>0.0249500460922718</v>
       </c>
       <c r="E186" s="0">
@@ -28630,7 +28630,7 @@
       <c r="C187" s="0" t="n">
         <v>0.33</v>
       </c>
-      <c r="D187" t="n">
+      <c r="D187" s="0" t="n">
         <v>0.02474693581461906</v>
       </c>
       <c r="E187" s="0">
@@ -28672,7 +28672,7 @@
       <c r="C188" s="0" t="n">
         <v>0.328</v>
       </c>
-      <c r="D188" t="n">
+      <c r="D188" s="0" t="n">
         <v>0.0247977115213871</v>
       </c>
       <c r="E188" s="0">
@@ -28714,7 +28714,7 @@
       <c r="C189" s="0" t="n">
         <v>0.327</v>
       </c>
-      <c r="D189" t="n">
+      <c r="D189" s="0" t="n">
         <v>0.02455391362309456</v>
       </c>
       <c r="E189" s="0">
@@ -28756,7 +28756,7 @@
       <c r="C190" s="0" t="n">
         <v>0.324</v>
       </c>
-      <c r="D190" t="n">
+      <c r="D190" s="0" t="n">
         <v>0.02486999705433846</v>
       </c>
       <c r="E190" s="0">
@@ -28798,7 +28798,7 @@
       <c r="C191" s="0" t="n">
         <v>0.322</v>
       </c>
-      <c r="D191" t="n">
+      <c r="D191" s="0" t="n">
         <v>0.02434824593365192</v>
       </c>
       <c r="E191" s="0">
@@ -28840,7 +28840,7 @@
       <c r="C192" s="0" t="n">
         <v>0.32</v>
       </c>
-      <c r="D192" t="n">
+      <c r="D192" s="0" t="n">
         <v>0.02544496022164822</v>
       </c>
       <c r="E192" s="0">
@@ -28882,7 +28882,7 @@
       <c r="C193" s="0" t="n">
         <v>0.317</v>
       </c>
-      <c r="D193" t="n">
+      <c r="D193" s="0" t="n">
         <v>0.02464304119348526</v>
       </c>
       <c r="E193" s="0">
@@ -28924,7 +28924,7 @@
       <c r="C194" s="0" t="n">
         <v>0.315</v>
       </c>
-      <c r="D194" t="n">
+      <c r="D194" s="0" t="n">
         <v>0.02476061508059502</v>
       </c>
       <c r="E194" s="0">
@@ -28966,7 +28966,7 @@
       <c r="C195" s="0" t="n">
         <v>0.313</v>
       </c>
-      <c r="D195" t="n">
+      <c r="D195" s="0" t="n">
         <v>0.02476061508059502</v>
       </c>
       <c r="E195" s="0">
@@ -29008,7 +29008,7 @@
       <c r="C196" s="0" t="n">
         <v>0.311</v>
       </c>
-      <c r="D196" t="n">
+      <c r="D196" s="0" t="n">
         <v>0.024</v>
       </c>
       <c r="E196" s="0">
@@ -29049,7 +29049,7 @@
       <c r="C197" s="0" t="n">
         <v>0.309</v>
       </c>
-      <c r="D197" t="n">
+      <c r="D197" s="0" t="n">
         <v>0.024</v>
       </c>
       <c r="E197" s="0">
@@ -29090,7 +29090,7 @@
       <c r="C198" s="0" t="n">
         <v>0.306</v>
       </c>
-      <c r="D198" t="n">
+      <c r="D198" s="0" t="n">
         <v>0.024</v>
       </c>
       <c r="E198" s="0">
@@ -29131,7 +29131,7 @@
       <c r="C199" s="0" t="n">
         <v>0.304</v>
       </c>
-      <c r="D199" t="n">
+      <c r="D199" s="0" t="n">
         <v>0.024</v>
       </c>
       <c r="E199" s="0">
@@ -29172,7 +29172,7 @@
       <c r="C200" s="0" t="n">
         <v>0.301</v>
       </c>
-      <c r="D200" t="n">
+      <c r="D200" s="0" t="n">
         <v>0.024</v>
       </c>
       <c r="E200" s="0">
@@ -29213,7 +29213,7 @@
       <c r="C201" s="0" t="n">
         <v>0.299</v>
       </c>
-      <c r="D201" t="n">
+      <c r="D201" s="0" t="n">
         <v>0.024</v>
       </c>
       <c r="E201" s="0">
@@ -29254,7 +29254,7 @@
       <c r="C202" s="0" t="n">
         <v>0.297</v>
       </c>
-      <c r="D202" t="n">
+      <c r="D202" s="0" t="n">
         <v>0.024</v>
       </c>
       <c r="E202" s="0">
@@ -29295,7 +29295,7 @@
       <c r="C203" s="0" t="n">
         <v>0.295</v>
       </c>
-      <c r="D203" t="n">
+      <c r="D203" s="0" t="n">
         <v>0.024</v>
       </c>
       <c r="E203" s="0">
@@ -29336,7 +29336,7 @@
       <c r="C204" s="0" t="n">
         <v>0.293</v>
       </c>
-      <c r="D204" t="n">
+      <c r="D204" s="0" t="n">
         <v>0.024</v>
       </c>
       <c r="E204" s="0">
@@ -29377,7 +29377,7 @@
       <c r="C205" s="0" t="n">
         <v>0.291</v>
       </c>
-      <c r="D205" t="n">
+      <c r="D205" s="0" t="n">
         <v>0.024</v>
       </c>
       <c r="E205" s="0">
@@ -29418,7 +29418,7 @@
       <c r="C206" s="0" t="n">
         <v>0.288</v>
       </c>
-      <c r="D206" t="n">
+      <c r="D206" s="0" t="n">
         <v>0.024</v>
       </c>
       <c r="E206" s="0">
@@ -29459,7 +29459,7 @@
       <c r="C207" s="0" t="n">
         <v>0.286</v>
       </c>
-      <c r="D207" t="n">
+      <c r="D207" s="0" t="n">
         <v>0.024</v>
       </c>
       <c r="E207" s="0">
@@ -29500,7 +29500,7 @@
       <c r="C208" s="0" t="n">
         <v>0.284</v>
       </c>
-      <c r="D208" t="n">
+      <c r="D208" s="0" t="n">
         <v>0.024</v>
       </c>
       <c r="E208" s="0">
@@ -29541,7 +29541,7 @@
       <c r="C209" s="0" t="n">
         <v>0.282</v>
       </c>
-      <c r="D209" t="n">
+      <c r="D209" s="0" t="n">
         <v>0.024</v>
       </c>
       <c r="E209" s="0">
@@ -29582,7 +29582,7 @@
       <c r="C210" s="0" t="n">
         <v>0.279</v>
       </c>
-      <c r="D210" t="n">
+      <c r="D210" s="0" t="n">
         <v>0.024</v>
       </c>
       <c r="E210" s="0">
@@ -29623,7 +29623,7 @@
       <c r="C211" s="0" t="n">
         <v>0.277</v>
       </c>
-      <c r="D211" t="n">
+      <c r="D211" s="0" t="n">
         <v>0.024</v>
       </c>
       <c r="E211" s="0">
@@ -29664,7 +29664,7 @@
       <c r="C212" s="0" t="n">
         <v>0.275</v>
       </c>
-      <c r="D212" t="n">
+      <c r="D212" s="0" t="n">
         <v>0.024</v>
       </c>
       <c r="E212" s="0">
@@ -29705,7 +29705,7 @@
       <c r="C213" s="0" t="n">
         <v>0.272</v>
       </c>
-      <c r="D213" t="n">
+      <c r="D213" s="0" t="n">
         <v>0.024</v>
       </c>
       <c r="E213" s="0">
@@ -29746,7 +29746,7 @@
       <c r="C214" s="0" t="n">
         <v>0.27</v>
       </c>
-      <c r="D214" t="n">
+      <c r="D214" s="0" t="n">
         <v>0.024</v>
       </c>
       <c r="E214" s="0">
@@ -29787,7 +29787,7 @@
       <c r="C215" s="0" t="n">
         <v>0.268</v>
       </c>
-      <c r="D215" t="n">
+      <c r="D215" s="0" t="n">
         <v>0.024</v>
       </c>
       <c r="E215" s="0">
@@ -29828,7 +29828,7 @@
       <c r="C216" s="0" t="n">
         <v>0.265</v>
       </c>
-      <c r="D216" t="n">
+      <c r="D216" s="0" t="n">
         <v>0.024</v>
       </c>
       <c r="E216" s="0">
@@ -29869,7 +29869,7 @@
       <c r="C217" s="0" t="n">
         <v>0.263</v>
       </c>
-      <c r="D217" t="n">
+      <c r="D217" s="0" t="n">
         <v>0.024</v>
       </c>
       <c r="E217" s="0">
@@ -29910,7 +29910,7 @@
       <c r="C218" s="0" t="n">
         <v>0.261</v>
       </c>
-      <c r="D218" t="n">
+      <c r="D218" s="0" t="n">
         <v>0.024</v>
       </c>
       <c r="E218" s="0">
@@ -29951,7 +29951,7 @@
       <c r="C219" s="0" t="n">
         <v>0.259</v>
       </c>
-      <c r="D219" t="n">
+      <c r="D219" s="0" t="n">
         <v>0.024</v>
       </c>
       <c r="E219" s="0">
@@ -29992,7 +29992,7 @@
       <c r="C220" s="0" t="n">
         <v>0.256</v>
       </c>
-      <c r="D220" t="n">
+      <c r="D220" s="0" t="n">
         <v>0.024</v>
       </c>
       <c r="E220" s="0">
@@ -30033,7 +30033,7 @@
       <c r="C221" s="0" t="n">
         <v>0.254</v>
       </c>
-      <c r="D221" t="n">
+      <c r="D221" s="0" t="n">
         <v>0.024</v>
       </c>
       <c r="E221" s="0">
@@ -30074,7 +30074,7 @@
       <c r="C222" s="0" t="n">
         <v>0.252</v>
       </c>
-      <c r="D222" t="n">
+      <c r="D222" s="0" t="n">
         <v>0.024</v>
       </c>
       <c r="E222" s="0">
@@ -30115,7 +30115,7 @@
       <c r="C223" s="0" t="n">
         <v>0.252</v>
       </c>
-      <c r="D223" t="n">
+      <c r="D223" s="0" t="n">
         <v>0.024</v>
       </c>
       <c r="E223" s="0">
